--- a/web/public/templates/vendors_sample.xlsx
+++ b/web/public/templates/vendors_sample.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,6 +534,64 @@
           <t>contact@metroads.example</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bright Outdoor Media</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Faisal Ahmed</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9800000004</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>faisal@brightoutdoor.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Prime Display Solutions</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Neha Bansal</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>9800000005</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>neha@primedisplay.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Signage Works</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9800000006</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/web/public/templates/vendors_sample.xlsx
+++ b/web/public/templates/vendors_sample.xlsx
@@ -446,19 +446,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -474,6 +475,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>contact_email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>remarks</t>
         </is>
       </c>
     </row>
@@ -498,6 +504,11 @@
           <t>ankit@sunrise.example</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Preferred vendor for West zone</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -520,6 +531,7 @@
           <t>rhea@skyline.example</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -534,6 +546,11 @@
           <t>contact@metroads.example</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Contact details pending</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -556,6 +573,7 @@
           <t>faisal@brightoutdoor.example</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -578,6 +596,11 @@
           <t>neha@primedisplay.example</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Handles boarding installs only</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -592,6 +615,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -604,12 +628,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -632,7 +656,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -642,7 +666,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vendor / company name.</t>
+          <t>Company name. Must be unique — an existing name is rejected rather than creating a second, indistinguishable vendor.</t>
         </is>
       </c>
     </row>
@@ -693,7 +717,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vendor email address.</t>
+          <t>Vendor email address. Optional, but must be valid and unique when given.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Free-text note about this vendor. Not used in any business rule; up to 2000 characters.</t>
         </is>
       </c>
     </row>

--- a/web/public/templates/vendors_sample.xlsx
+++ b/web/public/templates/vendors_sample.xlsx
@@ -531,7 +531,11 @@
           <t>rhea@skyline.example</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Boarding installs only</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -539,8 +543,16 @@
           <t>Metro Ads Co</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Imran Shaikh</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9800000003</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>contact@metroads.example</t>
@@ -548,7 +560,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Contact details pending</t>
+          <t>Onboarded Aug 2026</t>
         </is>
       </c>
     </row>
@@ -573,7 +585,11 @@
           <t>faisal@brightoutdoor.example</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Covers North zone</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -608,14 +624,26 @@
           <t>Coastal Signage Works</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Divya Nair</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>9800000006</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>divya@coastalsignage.example</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Coastal belt only</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -678,7 +706,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -695,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -712,7 +740,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -729,7 +757,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/web/public/templates/vendors_sample.xlsx
+++ b/web/public/templates/vendors_sample.xlsx
@@ -459,27 +459,27 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>COMPANY_NAME</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>CONTACT_PERSON</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>CONTACT_PHONE</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>CONTACT_EMAIL</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>REMARKS</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>COMPANY_NAME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>CONTACT_PERSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>CONTACT_PHONE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -735,7 +735,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>CONTACT_EMAIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>REMARKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/web/public/templates/vendors_sample.xlsx
+++ b/web/public/templates/vendors_sample.xlsx
@@ -73,12 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -656,117 +659,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Column names are matched on SPELLING ONLY. Upper or lower case makes no difference, and spaces, hyphens and underscores are treated the same - so CUST_CD, Cust_CD and "cust cd" are the same column. The headers on the Data sheet are all-caps; keep the wording, and the case is up to you. A sheet filled in with Caps Lock on uploads exactly like any other. Do not rename, reorder or delete columns - only the wording identifies them.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>COMPANY_NAME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Company name. Must be unique — an existing name is rejected rather than creating a second, indistinguishable vendor.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CONTACT_PERSON</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Primary contact person.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CONTACT_PHONE</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Contact phone number.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CONTACT_EMAIL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Vendor email address. Optional, but must be valid and unique when given.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Free-text note about this vendor. Not used in any business rule; up to 2000 characters.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>